--- a/public/templates/Site-Import-Template.xlsx
+++ b/public/templates/Site-Import-Template.xlsx
@@ -1,29 +1,22 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <TitlesOfParts>
-    <vt:vector size="4" baseType="lpstr">
-      <vt:lpstr>Instructions</vt:lpstr>
-      <vt:lpstr>Import Template</vt:lpstr>
-      <vt:lpstr>Sample Data</vt:lpstr>
-      <vt:lpstr>Lookup Lists</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14000" firstSheet="1" activeTab="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Import Template" sheetId="2" r:id="rId2"/>
+    <sheet name="Sample Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Lookup Lists" sheetId="4" r:id="rId4"/>
+  </sheets>
+  <calcPr calcId="191028"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:title>EHS360 Site Import Template</dc:title>
-  <dc:creator>Maitsys Assure</dc:creator>
-  <cp:lastModifiedBy>Maitsys Assure</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-01-01T00:00:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-01-01T00:00:00Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">EHS360 - Site Import Template</t>
@@ -250,7 +243,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
@@ -432,7 +425,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -715,24 +708,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14000" firstSheet="1" activeTab="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="Import Template" sheetId="2" r:id="rId2"/>
-    <sheet name="Sample Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Lookup Lists" sheetId="4" r:id="rId4"/>
-  </sheets>
-  <calcPr calcId="191028"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -928,7 +904,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1250,7 +1226,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr">
   <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1456,7 +1432,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
